--- a/ReferenceFiles/Sample Job Costing Sheet.xlsx
+++ b/ReferenceFiles/Sample Job Costing Sheet.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhatia\Desktop\CostEstimatorAgent\ReferenceFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF000AEB-4B76-407E-9453-FD2B585BE857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="142676- Structure Frame" sheetId="2" r:id="rId1"/>
@@ -12,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'142676- Structure Frame'!$A$1:$R$58</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="90">
   <si>
     <t>C&amp;J GULF EQUIPMENT MANUFACTURING L.L.C</t>
   </si>
@@ -69,21 +77,9 @@
     <t>PROJECT PACKAGE DETAILS</t>
   </si>
   <si>
-    <t>PIPING</t>
-  </si>
-  <si>
     <t>MODULE WORK</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>SKID MOUNTED PACKAGE</t>
-  </si>
-  <si>
-    <t>CEMENT LINING</t>
-  </si>
-  <si>
     <t>CUSTOMER P.O. Ref :</t>
   </si>
   <si>
@@ -183,9 +179,6 @@
     <t>Machining 8 labour hours per day for 4 days</t>
   </si>
   <si>
-    <t>1  Machinist</t>
-  </si>
-  <si>
     <t>Consumables</t>
   </si>
   <si>
@@ -213,13 +206,7 @@
     <t>SQM</t>
   </si>
   <si>
-    <t>1 Blaster 1 Helper</t>
-  </si>
-  <si>
     <t>Painting(6.65 Sq M per hour for 2 coat paint system)</t>
-  </si>
-  <si>
-    <t>1 Painter 1 Helper</t>
   </si>
   <si>
     <t>Third-Party Inspection (TPI)</t>
@@ -317,31 +304,19 @@
     <t>M20X90 Long Bolts HEX HD &amp; Nut to BS 4190 Gr.8.8</t>
   </si>
   <si>
-    <t>2 Fabricator 2 Helper</t>
-  </si>
-  <si>
-    <t>2 Welder</t>
-  </si>
-  <si>
     <t>Structural Welding considering 16 labor hours per day for 10  Days</t>
   </si>
   <si>
     <t>Structuralt Fabrication considering 32 labor hours per day for 10 Days</t>
   </si>
   <si>
-    <t>REF NO: CNJ/142676/01/2025</t>
-  </si>
-  <si>
-    <t>Descon Engineering</t>
-  </si>
-  <si>
-    <t>Mr. Harun Khan</t>
+    <t xml:space="preserve">REF NO: </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -1046,7 +1021,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1186,25 +1161,332 @@
     <xf numFmtId="2" fontId="20" fillId="3" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="3" borderId="25" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="40" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="26" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1222,30 +1504,12 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1258,322 +1522,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="26" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="40" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="20" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="6"/>
+    <cellStyle name="Comma 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="4"/>
-    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1609,7 +1565,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6CB3B0-52D4-4BFB-B1AD-6FEC0F2084B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6CB3B0-52D4-4BFB-B1AD-6FEC0F2084B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1931,18 +1887,18 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
@@ -1966,43 +1922,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="154" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="156"/>
+      <c r="A1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="61"/>
     </row>
     <row r="2" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="157" t="s">
+      <c r="E2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -2010,336 +1966,318 @@
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="158" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="159"/>
-      <c r="O3" s="159"/>
-      <c r="P3" s="159"/>
-      <c r="Q3" s="159"/>
-      <c r="R3" s="160"/>
+      <c r="A3" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="65"/>
     </row>
     <row r="4" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="68" t="s">
-        <v>99</v>
-      </c>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
       <c r="D4" s="69"/>
-      <c r="E4" s="145" t="s">
+      <c r="E4" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="141"/>
-      <c r="G4" s="161">
-        <v>45686</v>
-      </c>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
       <c r="H4" s="69"/>
       <c r="I4" s="69"/>
       <c r="J4" s="69"/>
       <c r="K4" s="69"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="145" t="s">
+      <c r="L4" s="73"/>
+      <c r="M4" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="145"/>
-      <c r="O4" s="68">
-        <v>142676</v>
-      </c>
+      <c r="N4" s="70"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="69"/>
       <c r="Q4" s="69"/>
-      <c r="R4" s="70"/>
+      <c r="R4" s="73"/>
     </row>
     <row r="5" spans="1:19" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="150"/>
-      <c r="E5" s="140" t="s">
+      <c r="B5" s="85"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="141"/>
-      <c r="G5" s="68" t="s">
-        <v>100</v>
-      </c>
+      <c r="F5" s="71"/>
+      <c r="G5" s="68"/>
       <c r="H5" s="69"/>
       <c r="I5" s="69"/>
       <c r="J5" s="69"/>
       <c r="K5" s="69"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="145" t="s">
+      <c r="L5" s="73"/>
+      <c r="M5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="145"/>
-      <c r="O5" s="151"/>
-      <c r="P5" s="152"/>
-      <c r="Q5" s="152"/>
-      <c r="R5" s="153"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="88"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="90"/>
     </row>
     <row r="6" spans="1:19" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="139"/>
-      <c r="E6" s="140" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="141"/>
-      <c r="G6" s="142">
-        <v>971566529515</v>
-      </c>
-      <c r="H6" s="143"/>
-      <c r="I6" s="143"/>
-      <c r="J6" s="143"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="144"/>
-      <c r="M6" s="145" t="s">
+      <c r="F6" s="71"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="145"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="147"/>
-      <c r="Q6" s="147"/>
-      <c r="R6" s="148"/>
-    </row>
-    <row r="7" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="108" t="s">
+      <c r="N6" s="70"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
+      <c r="R6" s="84"/>
+    </row>
+    <row r="7" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="B7" s="85"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="6"/>
       <c r="E7" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="73"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="100"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="73"/>
+    </row>
+    <row r="8" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="91"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="99"/>
+    </row>
+    <row r="9" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="70"/>
-      <c r="G7" s="133" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="134"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="135" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="135"/>
-      <c r="L7" s="134"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="136"/>
-      <c r="O7" s="137" t="s">
-        <v>16</v>
-      </c>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="70"/>
-    </row>
-    <row r="8" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="128"/>
-      <c r="M8" s="129"/>
-      <c r="N8" s="129"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="132"/>
-    </row>
-    <row r="9" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="122" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="123"/>
+      <c r="B9" s="75"/>
       <c r="C9" s="68"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="112"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="67"/>
       <c r="G9" s="68"/>
       <c r="H9" s="69"/>
       <c r="I9" s="69"/>
       <c r="J9" s="69"/>
       <c r="K9" s="69"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="119"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="121"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="106"/>
+      <c r="Q9" s="106"/>
+      <c r="R9" s="107"/>
     </row>
     <row r="10" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="108" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="109"/>
+      <c r="A10" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="85"/>
       <c r="C10" s="68"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="112"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67"/>
       <c r="G10" s="68"/>
       <c r="H10" s="69"/>
       <c r="I10" s="69"/>
       <c r="J10" s="69"/>
       <c r="K10" s="69"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="109"/>
-      <c r="O10" s="119"/>
-      <c r="P10" s="120"/>
-      <c r="Q10" s="120"/>
-      <c r="R10" s="121"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="106"/>
+      <c r="R10" s="107"/>
     </row>
     <row r="11" spans="1:19" ht="22.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="108" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="109"/>
+      <c r="A11" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="85"/>
       <c r="C11" s="68"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="108" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="112"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="67"/>
       <c r="G11" s="68"/>
       <c r="H11" s="69"/>
       <c r="I11" s="69"/>
       <c r="J11" s="69"/>
       <c r="K11" s="69"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="117"/>
-      <c r="Q11" s="117"/>
-      <c r="R11" s="118"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="113"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="115"/>
     </row>
     <row r="12" spans="1:19" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="108" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="109"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="112"/>
+      <c r="A12" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="85"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="67"/>
       <c r="G12" s="68"/>
       <c r="H12" s="69"/>
       <c r="I12" s="69"/>
       <c r="J12" s="69"/>
       <c r="K12" s="69"/>
-      <c r="L12" s="70"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="109"/>
-      <c r="O12" s="113"/>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="114"/>
-      <c r="R12" s="115"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="112"/>
     </row>
     <row r="13" spans="1:19" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="100" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="101"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="101"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="N13" s="101"/>
-      <c r="O13" s="101"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="102"/>
+      <c r="A13" s="120"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="121"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="120" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="121"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="120" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="121"/>
+      <c r="R13" s="122"/>
     </row>
     <row r="14" spans="1:19" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="123" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="J14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="10" t="s">
+      <c r="K14" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="L14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="M14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="103" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" s="105"/>
+      <c r="R14" s="125"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
-      <c r="B15" s="106" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
+      <c r="B15" s="126" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
       <c r="G15" s="12"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
@@ -2350,25 +2288,23 @@
       <c r="N15" s="18"/>
       <c r="O15" s="18"/>
       <c r="P15" s="18"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="83"/>
+      <c r="Q15" s="118"/>
+      <c r="R15" s="119"/>
     </row>
     <row r="16" spans="1:19" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>1</v>
       </c>
-      <c r="B16" s="80" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="23">
-        <v>0</v>
-      </c>
+      <c r="B16" s="116" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="25"/>
@@ -2381,26 +2317,24 @@
       <c r="N16" s="18"/>
       <c r="O16" s="18"/>
       <c r="P16" s="18"/>
-      <c r="Q16" s="82"/>
-      <c r="R16" s="83"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="119"/>
       <c r="S16"/>
     </row>
     <row r="17" spans="1:19" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B17" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="23">
-        <v>0</v>
-      </c>
+      <c r="B17" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="23"/>
       <c r="H17" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I17" s="24"/>
       <c r="J17" s="25"/>
@@ -2413,26 +2347,24 @@
       <c r="N17" s="18"/>
       <c r="O17" s="18"/>
       <c r="P17" s="18"/>
-      <c r="Q17" s="82"/>
-      <c r="R17" s="83"/>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="119"/>
       <c r="S17"/>
     </row>
     <row r="18" spans="1:19" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>2</v>
       </c>
-      <c r="B18" s="80" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="23">
-        <v>0</v>
-      </c>
+      <c r="B18" s="116" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="23"/>
       <c r="H18" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I18" s="24"/>
       <c r="J18" s="25"/>
@@ -2445,26 +2377,24 @@
       <c r="N18" s="18"/>
       <c r="O18" s="18"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="82"/>
-      <c r="R18" s="83"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="119"/>
       <c r="S18"/>
     </row>
     <row r="19" spans="1:19" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>2.1</v>
       </c>
-      <c r="B19" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="23">
-        <v>0</v>
-      </c>
+      <c r="B19" s="116" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I19" s="24"/>
       <c r="J19" s="25"/>
@@ -2477,26 +2407,24 @@
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="83"/>
+      <c r="Q19" s="118"/>
+      <c r="R19" s="119"/>
       <c r="S19"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>3</v>
       </c>
-      <c r="B20" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="23">
-        <v>0</v>
-      </c>
+      <c r="B20" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="23"/>
       <c r="H20" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I20" s="24"/>
       <c r="J20" s="25"/>
@@ -2509,26 +2437,24 @@
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
       <c r="P20" s="18"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="83"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="119"/>
       <c r="S20"/>
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>4</v>
       </c>
-      <c r="B21" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="23">
-        <v>0</v>
-      </c>
+      <c r="B21" s="116" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I21" s="24"/>
       <c r="J21" s="25"/>
@@ -2541,28 +2467,28 @@
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="18"/>
-      <c r="Q21" s="82"/>
-      <c r="R21" s="83"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="119"/>
       <c r="S21"/>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>5</v>
       </c>
-      <c r="B22" s="98" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="99" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="99" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="99" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="168"/>
-      <c r="G22" s="53"/>
+      <c r="B22" s="128" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="130"/>
+      <c r="G22" s="51"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
       <c r="J22" s="25"/>
@@ -2575,25 +2501,23 @@
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
       <c r="P22" s="18"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="83"/>
+      <c r="Q22" s="118"/>
+      <c r="R22" s="119"/>
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B23" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="164"/>
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
-      <c r="F23" s="170"/>
-      <c r="G23" s="53">
-        <v>7802.27</v>
-      </c>
+      <c r="B23" s="131" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="132"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="51"/>
       <c r="H23" s="24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I23" s="24"/>
       <c r="J23" s="25">
@@ -2601,32 +2525,30 @@
       </c>
       <c r="K23" s="26">
         <f t="shared" si="0"/>
-        <v>31209.08</v>
+        <v>0</v>
       </c>
       <c r="L23" s="27"/>
       <c r="M23" s="17"/>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
       <c r="P23" s="18"/>
-      <c r="Q23" s="82"/>
-      <c r="R23" s="83"/>
+      <c r="Q23" s="118"/>
+      <c r="R23" s="119"/>
     </row>
     <row r="24" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="29">
         <v>5.2</v>
       </c>
-      <c r="B24" s="169" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="164"/>
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="170"/>
-      <c r="G24" s="53">
-        <v>30</v>
-      </c>
+      <c r="B24" s="131" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="132"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="51"/>
       <c r="H24" s="24" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I24" s="24"/>
       <c r="J24" s="25">
@@ -2634,32 +2556,30 @@
       </c>
       <c r="K24" s="26">
         <f t="shared" si="0"/>
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="L24" s="27"/>
       <c r="M24" s="17"/>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
       <c r="P24" s="18"/>
-      <c r="Q24" s="56"/>
-      <c r="R24" s="57"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="20"/>
     </row>
     <row r="25" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>5.3</v>
       </c>
-      <c r="B25" s="165" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="166"/>
-      <c r="D25" s="166"/>
-      <c r="E25" s="166"/>
-      <c r="F25" s="167"/>
-      <c r="G25" s="53">
-        <v>120</v>
-      </c>
+      <c r="B25" s="134" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="135"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="51"/>
       <c r="H25" s="24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="25">
@@ -2667,32 +2587,30 @@
       </c>
       <c r="K25" s="26">
         <f t="shared" si="0"/>
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="L25" s="27"/>
       <c r="M25" s="30"/>
       <c r="N25" s="18"/>
       <c r="O25" s="18"/>
       <c r="P25" s="18"/>
-      <c r="Q25" s="51"/>
-      <c r="R25" s="52"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="20"/>
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>6</v>
       </c>
-      <c r="B26" s="98" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="23">
-        <v>0</v>
-      </c>
+      <c r="B26" s="128" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="129"/>
+      <c r="D26" s="129"/>
+      <c r="E26" s="129"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="23"/>
       <c r="H26" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I26" s="24"/>
       <c r="J26" s="25"/>
@@ -2705,17 +2623,17 @@
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
       <c r="P26" s="18"/>
-      <c r="Q26" s="82"/>
-      <c r="R26" s="83"/>
+      <c r="Q26" s="118"/>
+      <c r="R26" s="119"/>
       <c r="S26"/>
     </row>
     <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
-      <c r="B27" s="171"/>
-      <c r="C27" s="172"/>
-      <c r="D27" s="172"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="173"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="55"/>
       <c r="G27" s="23"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -2729,21 +2647,21 @@
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
       <c r="P27" s="18"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="57"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="20"/>
       <c r="S27"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
-      <c r="B28" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="97"/>
+      <c r="B28" s="116" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="140"/>
       <c r="G28" s="23"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
@@ -2764,39 +2682,33 @@
       <c r="A29" s="29">
         <v>7.1</v>
       </c>
-      <c r="B29" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="96"/>
-      <c r="G29" s="53">
-        <v>7802.27</v>
-      </c>
+      <c r="B29" s="137" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="139"/>
+      <c r="G29" s="51"/>
       <c r="H29" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I29" s="48">
-        <v>160</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I29" s="48"/>
       <c r="J29" s="31">
         <v>10.5</v>
       </c>
       <c r="K29" s="26">
         <f>I29*J29</f>
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="L29" s="27"/>
-      <c r="M29" s="17" t="s">
-        <v>95</v>
-      </c>
+      <c r="M29" s="17"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
       <c r="P29" s="18"/>
@@ -2804,46 +2716,40 @@
       <c r="R29" s="20"/>
       <c r="S29" s="1">
         <f>230000/30/30*(I29/8)</f>
-        <v>5111.1111111111113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29">
         <v>7.2</v>
       </c>
-      <c r="B30" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="96"/>
-      <c r="G30" s="53">
-        <v>7802.27</v>
-      </c>
+      <c r="B30" s="137" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="139"/>
+      <c r="G30" s="51"/>
       <c r="H30" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="48">
-        <v>320</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I30" s="48"/>
       <c r="J30" s="31">
         <v>9.5</v>
       </c>
       <c r="K30" s="26">
         <f>I30*J30</f>
-        <v>3040</v>
+        <v>0</v>
       </c>
       <c r="L30" s="27"/>
-      <c r="M30" s="17" t="s">
-        <v>94</v>
-      </c>
+      <c r="M30" s="17"/>
       <c r="N30" s="18"/>
       <c r="O30" s="18"/>
       <c r="P30" s="18"/>
@@ -2851,23 +2757,23 @@
       <c r="R30" s="20"/>
       <c r="S30" s="1">
         <f>230000/30/30*(I30/8)</f>
-        <v>10222.222222222223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29">
         <v>7.3</v>
       </c>
-      <c r="B31" s="162" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="163"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="163"/>
-      <c r="F31" s="163"/>
+      <c r="B31" s="141" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="142"/>
+      <c r="D31" s="142"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
       <c r="G31" s="34"/>
       <c r="H31" s="24" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I31" s="48"/>
       <c r="J31" s="31">
@@ -2893,16 +2799,16 @@
       <c r="A32" s="29">
         <v>7.4</v>
       </c>
-      <c r="B32" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="64"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
+      <c r="B32" s="137" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
       <c r="G32" s="23"/>
       <c r="H32" s="24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I32" s="24"/>
       <c r="J32" s="31">
@@ -2913,9 +2819,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="27"/>
-      <c r="M32" s="17" t="s">
-        <v>50</v>
-      </c>
+      <c r="M32" s="17"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
       <c r="P32" s="18"/>
@@ -2927,26 +2831,24 @@
         <v>8</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
-      <c r="G33" s="23">
-        <v>1</v>
-      </c>
+      <c r="G33" s="23"/>
       <c r="H33" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I33" s="24"/>
       <c r="J33" s="25">
         <f>D58/20</f>
-        <v>5348.3099999999995</v>
+        <v>0</v>
       </c>
       <c r="K33" s="26">
         <f t="shared" si="0"/>
-        <v>5348.3099999999995</v>
+        <v>0</v>
       </c>
       <c r="L33" s="27"/>
       <c r="M33" s="17"/>
@@ -2960,13 +2862,13 @@
       <c r="A34" s="11">
         <v>9</v>
       </c>
-      <c r="B34" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="81"/>
+      <c r="B34" s="116" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="117"/>
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="117"/>
       <c r="G34" s="23"/>
       <c r="H34" s="24"/>
       <c r="I34" s="24"/>
@@ -2987,18 +2889,16 @@
       <c r="A35" s="29">
         <v>9.1</v>
       </c>
-      <c r="B35" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="23">
-        <v>0</v>
-      </c>
+      <c r="B35" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="23"/>
       <c r="H35" s="24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I35" s="24"/>
       <c r="J35" s="25">
@@ -3021,13 +2921,13 @@
       <c r="A36" s="11">
         <v>10</v>
       </c>
-      <c r="B36" s="80" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
+      <c r="B36" s="116" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
       <c r="G36" s="34"/>
       <c r="H36" s="35"/>
       <c r="I36" s="35"/>
@@ -3049,18 +2949,16 @@
       <c r="A37" s="29">
         <v>10.1</v>
       </c>
-      <c r="B37" s="63" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="64"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="34">
-        <v>10</v>
-      </c>
+      <c r="B37" s="137" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="138"/>
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="34"/>
       <c r="H37" s="35" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="31">
@@ -3068,7 +2966,7 @@
       </c>
       <c r="K37" s="26">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="L37" s="27"/>
       <c r="M37" s="17"/>
@@ -3082,13 +2980,13 @@
       <c r="A38" s="11">
         <v>11</v>
       </c>
-      <c r="B38" s="80" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="81"/>
+      <c r="B38" s="116" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
       <c r="G38" s="23"/>
       <c r="H38" s="24"/>
       <c r="I38" s="24"/>
@@ -3109,18 +3007,16 @@
       <c r="A39" s="29">
         <v>11.1</v>
       </c>
-      <c r="B39" s="63" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="23">
-        <v>0</v>
-      </c>
+      <c r="B39" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="138"/>
+      <c r="D39" s="138"/>
+      <c r="E39" s="138"/>
+      <c r="F39" s="138"/>
+      <c r="G39" s="23"/>
       <c r="H39" s="24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="25">
@@ -3139,41 +3035,34 @@
       <c r="R39" s="20"/>
       <c r="S39" s="1">
         <f>230000/30/30*(I40/8)</f>
-        <v>1441.1027568922307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="29">
         <v>11.2</v>
       </c>
-      <c r="B40" s="94" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
-      <c r="F40" s="95"/>
-      <c r="G40" s="34">
-        <v>200</v>
-      </c>
+      <c r="B40" s="143" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="144"/>
+      <c r="D40" s="144"/>
+      <c r="E40" s="144"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="34"/>
       <c r="H40" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="I40" s="37">
-        <f>1/13.3*G40*3</f>
-        <v>45.112781954887218</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I40" s="37"/>
       <c r="J40" s="31">
         <v>9</v>
       </c>
       <c r="K40" s="26">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="L40" s="27"/>
-      <c r="M40" s="17" t="s">
-        <v>60</v>
-      </c>
+      <c r="M40" s="17"/>
       <c r="N40" s="18"/>
       <c r="O40" s="18"/>
       <c r="P40" s="18"/>
@@ -3181,41 +3070,34 @@
       <c r="R40" s="20"/>
       <c r="S40" s="1">
         <f>230000/30/30*(I41/8)</f>
-        <v>2882.2055137844613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="29">
         <v>11.3</v>
       </c>
-      <c r="B41" s="94" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="95"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="34">
-        <v>200</v>
-      </c>
+      <c r="B41" s="143" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="144"/>
+      <c r="D41" s="144"/>
+      <c r="E41" s="144"/>
+      <c r="F41" s="144"/>
+      <c r="G41" s="34"/>
       <c r="H41" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="I41" s="37">
-        <f>1/6.65*G41*3</f>
-        <v>90.225563909774436</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I41" s="37"/>
       <c r="J41" s="31">
         <v>11</v>
       </c>
       <c r="K41" s="26">
         <f t="shared" si="0"/>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="L41" s="27"/>
-      <c r="M41" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="M41" s="17"/>
       <c r="N41" s="18"/>
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
@@ -3227,18 +3109,16 @@
       <c r="A42" s="11">
         <v>12</v>
       </c>
-      <c r="B42" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="81"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="23">
-        <v>0</v>
-      </c>
+      <c r="B42" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="23"/>
       <c r="H42" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I42" s="24"/>
       <c r="J42" s="25"/>
@@ -3251,25 +3131,23 @@
       <c r="N42" s="18"/>
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
-      <c r="Q42" s="82"/>
-      <c r="R42" s="83"/>
+      <c r="Q42" s="118"/>
+      <c r="R42" s="119"/>
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>13</v>
       </c>
-      <c r="B43" s="80" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="81"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="23">
-        <v>1</v>
-      </c>
+      <c r="B43" s="116" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="23"/>
       <c r="H43" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I43" s="24"/>
       <c r="J43" s="25">
@@ -3277,7 +3155,7 @@
       </c>
       <c r="K43" s="26">
         <f t="shared" si="2"/>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L43" s="27"/>
       <c r="M43" s="17"/>
@@ -3291,18 +3169,16 @@
       <c r="A44" s="11">
         <v>14</v>
       </c>
-      <c r="B44" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="23">
-        <v>1</v>
-      </c>
+      <c r="B44" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="23"/>
       <c r="H44" s="24" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="25">
@@ -3310,7 +3186,7 @@
       </c>
       <c r="K44" s="26">
         <f t="shared" si="2"/>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L44" s="40"/>
       <c r="M44" s="17"/>
@@ -3326,17 +3202,15 @@
         <v>16</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C45" s="22"/>
       <c r="D45" s="22"/>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
-      <c r="G45" s="23">
-        <v>0</v>
-      </c>
+      <c r="G45" s="23"/>
       <c r="H45" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="25"/>
@@ -3357,18 +3231,16 @@
       <c r="A46" s="11">
         <v>17</v>
       </c>
-      <c r="B46" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="81"/>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="23">
-        <v>0</v>
-      </c>
+      <c r="B46" s="116" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="117"/>
+      <c r="D46" s="117"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="23"/>
       <c r="H46" s="24" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="25"/>
@@ -3381,26 +3253,24 @@
       <c r="N46" s="18"/>
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
-      <c r="Q46" s="82"/>
-      <c r="R46" s="83"/>
+      <c r="Q46" s="118"/>
+      <c r="R46" s="119"/>
       <c r="S46"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>18</v>
       </c>
-      <c r="B47" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="81"/>
-      <c r="D47" s="81"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="23">
-        <v>0</v>
-      </c>
+      <c r="B47" s="116" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="23"/>
       <c r="H47" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="25"/>
@@ -3413,26 +3283,24 @@
       <c r="N47" s="18"/>
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
-      <c r="Q47" s="82"/>
-      <c r="R47" s="83"/>
+      <c r="Q47" s="118"/>
+      <c r="R47" s="119"/>
       <c r="S47"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>20</v>
       </c>
-      <c r="B48" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="81"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="23">
-        <v>0</v>
-      </c>
+      <c r="B48" s="116" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="117"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="23"/>
       <c r="H48" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I48" s="24"/>
       <c r="J48" s="25"/>
@@ -3445,26 +3313,24 @@
       <c r="N48" s="18"/>
       <c r="O48" s="18"/>
       <c r="P48" s="18"/>
-      <c r="Q48" s="82"/>
-      <c r="R48" s="83"/>
+      <c r="Q48" s="118"/>
+      <c r="R48" s="119"/>
       <c r="S48"/>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>21</v>
       </c>
-      <c r="B49" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="81"/>
-      <c r="D49" s="81"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="23">
-        <v>0</v>
-      </c>
+      <c r="B49" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="23"/>
       <c r="H49" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="25"/>
@@ -3477,26 +3343,24 @@
       <c r="N49" s="18"/>
       <c r="O49" s="18"/>
       <c r="P49" s="18"/>
-      <c r="Q49" s="82"/>
-      <c r="R49" s="83"/>
+      <c r="Q49" s="118"/>
+      <c r="R49" s="119"/>
       <c r="S49"/>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>22</v>
       </c>
-      <c r="B50" s="80" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="23">
-        <v>0</v>
-      </c>
+      <c r="B50" s="116" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="117"/>
+      <c r="D50" s="117"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="23"/>
       <c r="H50" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I50" s="24"/>
       <c r="J50" s="25"/>
@@ -3509,26 +3373,24 @@
       <c r="N50" s="18"/>
       <c r="O50" s="18"/>
       <c r="P50" s="18"/>
-      <c r="Q50" s="82"/>
-      <c r="R50" s="83"/>
+      <c r="Q50" s="118"/>
+      <c r="R50" s="119"/>
       <c r="S50"/>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>23</v>
       </c>
-      <c r="B51" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="81"/>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="23">
-        <v>0</v>
-      </c>
+      <c r="B51" s="116" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="23"/>
       <c r="H51" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I51" s="24"/>
       <c r="J51" s="25"/>
@@ -3541,26 +3403,24 @@
       <c r="N51" s="18"/>
       <c r="O51" s="18"/>
       <c r="P51" s="18"/>
-      <c r="Q51" s="82"/>
-      <c r="R51" s="83"/>
+      <c r="Q51" s="118"/>
+      <c r="R51" s="119"/>
       <c r="S51"/>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>24</v>
       </c>
-      <c r="B52" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="23">
-        <v>0</v>
-      </c>
+      <c r="B52" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="23"/>
       <c r="H52" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I52" s="24"/>
       <c r="J52" s="25"/>
@@ -3573,26 +3433,24 @@
       <c r="N52" s="18"/>
       <c r="O52" s="18"/>
       <c r="P52" s="18"/>
-      <c r="Q52" s="82"/>
-      <c r="R52" s="83"/>
+      <c r="Q52" s="118"/>
+      <c r="R52" s="119"/>
       <c r="S52"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>25</v>
       </c>
-      <c r="B53" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" s="81"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="23">
-        <v>0</v>
-      </c>
+      <c r="B53" s="116" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="117"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="23"/>
       <c r="H53" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I53" s="24"/>
       <c r="J53" s="25"/>
@@ -3605,26 +3463,24 @@
       <c r="N53" s="18"/>
       <c r="O53" s="18"/>
       <c r="P53" s="18"/>
-      <c r="Q53" s="82"/>
-      <c r="R53" s="83"/>
+      <c r="Q53" s="118"/>
+      <c r="R53" s="119"/>
       <c r="S53"/>
     </row>
     <row r="54" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>26</v>
       </c>
-      <c r="B54" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" s="81"/>
-      <c r="D54" s="81"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="81"/>
-      <c r="G54" s="23">
-        <v>0</v>
-      </c>
+      <c r="B54" s="116" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="117"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="23"/>
       <c r="H54" s="24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I54" s="24"/>
       <c r="J54" s="38"/>
@@ -3637,152 +3493,150 @@
       <c r="N54" s="18"/>
       <c r="O54" s="18"/>
       <c r="P54" s="18"/>
-      <c r="Q54" s="82"/>
-      <c r="R54" s="83"/>
+      <c r="Q54" s="118"/>
+      <c r="R54" s="119"/>
       <c r="S54" s="1">
         <f>SUM(S15:S43)</f>
-        <v>19656.641604010027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" s="85"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="86">
+      <c r="A55" s="151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="152"/>
+      <c r="C55" s="152"/>
+      <c r="D55" s="153">
         <f>SUM(K16:K54)</f>
-        <v>60172.39</v>
-      </c>
-      <c r="E55" s="87"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="H55" s="89"/>
+        <v>0</v>
+      </c>
+      <c r="E55" s="154"/>
+      <c r="F55" s="155"/>
+      <c r="G55" s="156" t="s">
+        <v>71</v>
+      </c>
+      <c r="H55" s="156"/>
       <c r="I55" s="41"/>
-      <c r="J55" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="K55" s="174"/>
-      <c r="L55" s="55"/>
-      <c r="M55" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="N55" s="91"/>
-      <c r="O55" s="91"/>
-      <c r="P55" s="92" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q55" s="90"/>
-      <c r="R55" s="93"/>
+      <c r="J55" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K55" s="56"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="157" t="s">
+        <v>73</v>
+      </c>
+      <c r="N55" s="158"/>
+      <c r="O55" s="158"/>
+      <c r="P55" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q55" s="157"/>
+      <c r="R55" s="160"/>
     </row>
     <row r="56" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="75" t="s">
-        <v>81</v>
-      </c>
-      <c r="B56" s="76"/>
-      <c r="C56" s="76"/>
-      <c r="D56" s="77">
+      <c r="A56" s="145" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="146"/>
+      <c r="C56" s="146"/>
+      <c r="D56" s="147">
         <f>S54</f>
-        <v>19656.641604010027</v>
-      </c>
-      <c r="E56" s="78"/>
-      <c r="F56" s="79"/>
-      <c r="G56" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="H56" s="66"/>
+        <v>0</v>
+      </c>
+      <c r="E56" s="148"/>
+      <c r="F56" s="149"/>
+      <c r="G56" s="150" t="s">
+        <v>75</v>
+      </c>
+      <c r="H56" s="150"/>
       <c r="I56" s="42"/>
-      <c r="J56" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="K56" s="174"/>
-      <c r="L56" s="55"/>
-      <c r="M56" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="N56" s="66"/>
-      <c r="O56" s="66"/>
+      <c r="J56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K56" s="56"/>
+      <c r="L56" s="52"/>
+      <c r="M56" s="150" t="s">
+        <v>75</v>
+      </c>
+      <c r="N56" s="150"/>
+      <c r="O56" s="150"/>
       <c r="P56" s="68" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Q56" s="69"/>
-      <c r="R56" s="70"/>
+      <c r="R56" s="73"/>
     </row>
     <row r="57" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="58" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" s="59"/>
-      <c r="C57" s="59"/>
-      <c r="D57" s="60">
+      <c r="A57" s="161" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="162"/>
+      <c r="C57" s="162"/>
+      <c r="D57" s="163">
         <f>D55+D56</f>
-        <v>79829.03160401003</v>
-      </c>
-      <c r="E57" s="61"/>
-      <c r="F57" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="E57" s="164"/>
+      <c r="F57" s="165"/>
       <c r="G57" s="43"/>
       <c r="H57" s="43"/>
       <c r="I57" s="43"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="174"/>
-      <c r="L57" s="55"/>
-      <c r="M57" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="N57" s="66"/>
-      <c r="O57" s="67"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="56"/>
+      <c r="L57" s="52"/>
+      <c r="M57" s="166" t="s">
+        <v>78</v>
+      </c>
+      <c r="N57" s="150"/>
+      <c r="O57" s="167"/>
       <c r="P57" s="68" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q57" s="69"/>
-      <c r="R57" s="70"/>
+      <c r="R57" s="73"/>
     </row>
     <row r="58" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58" s="59"/>
-      <c r="C58" s="59"/>
-      <c r="D58" s="60">
-        <v>106966.2</v>
-      </c>
-      <c r="E58" s="61"/>
-      <c r="F58" s="62"/>
-      <c r="G58" s="71"/>
-      <c r="H58" s="71"/>
+      <c r="A58" s="161" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="162"/>
+      <c r="C58" s="162"/>
+      <c r="D58" s="163"/>
+      <c r="E58" s="164"/>
+      <c r="F58" s="165"/>
+      <c r="G58" s="168"/>
+      <c r="H58" s="168"/>
       <c r="I58" s="43"/>
-      <c r="J58" s="54"/>
-      <c r="K58" s="174"/>
-      <c r="L58" s="55"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="56"/>
+      <c r="L58" s="52"/>
       <c r="M58" s="68"/>
       <c r="N58" s="69"/>
-      <c r="O58" s="70"/>
-      <c r="P58" s="72"/>
-      <c r="Q58" s="73"/>
-      <c r="R58" s="74"/>
+      <c r="O58" s="73"/>
+      <c r="P58" s="169"/>
+      <c r="Q58" s="170"/>
+      <c r="R58" s="171"/>
       <c r="T58"/>
     </row>
     <row r="59" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="58" t="s">
-        <v>88</v>
-      </c>
-      <c r="B59" s="59"/>
-      <c r="C59" s="59"/>
-      <c r="D59" s="60">
+      <c r="A59" s="161" t="s">
+        <v>81</v>
+      </c>
+      <c r="B59" s="162"/>
+      <c r="C59" s="162"/>
+      <c r="D59" s="163">
         <f>+D58-D57</f>
-        <v>27137.168395989967</v>
-      </c>
-      <c r="E59" s="61"/>
-      <c r="F59" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="E59" s="164"/>
+      <c r="F59" s="165"/>
       <c r="G59"/>
       <c r="H59"/>
       <c r="I59"/>
-      <c r="J59" s="175"/>
-      <c r="K59" s="176"/>
-      <c r="L59" s="175"/>
-      <c r="M59" s="175"/>
+      <c r="J59"/>
+      <c r="K59" s="57"/>
+      <c r="L59"/>
+      <c r="M59"/>
       <c r="N59"/>
       <c r="O59"/>
       <c r="P59"/>
@@ -3799,10 +3653,10 @@
       <c r="G60"/>
       <c r="H60"/>
       <c r="I60"/>
-      <c r="J60" s="175"/>
-      <c r="K60" s="176"/>
-      <c r="L60" s="175"/>
-      <c r="M60" s="175"/>
+      <c r="J60"/>
+      <c r="K60" s="57"/>
+      <c r="L60"/>
+      <c r="M60"/>
       <c r="N60"/>
       <c r="O60"/>
       <c r="P60"/>
@@ -3815,17 +3669,17 @@
       <c r="B61"/>
       <c r="C61"/>
       <c r="E61"/>
-      <c r="F61" s="49">
+      <c r="F61" s="49" t="e">
         <f>D59/D58</f>
-        <v>0.25369853650957003</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
       <c r="I61"/>
-      <c r="J61" s="175"/>
-      <c r="K61" s="176"/>
-      <c r="L61" s="175"/>
-      <c r="M61" s="175"/>
+      <c r="J61"/>
+      <c r="K61" s="57"/>
+      <c r="L61"/>
+      <c r="M61"/>
       <c r="N61"/>
       <c r="O61"/>
       <c r="P61"/>
@@ -3837,7 +3691,7 @@
       <c r="A62" s="45"/>
       <c r="B62" s="36">
         <f>D58-D55</f>
-        <v>46793.81</v>
+        <v>0</v>
       </c>
       <c r="C62"/>
       <c r="D62" s="36"/>
@@ -3846,10 +3700,10 @@
       <c r="G62"/>
       <c r="H62" s="36"/>
       <c r="I62"/>
-      <c r="J62" s="175"/>
-      <c r="K62" s="176"/>
-      <c r="L62" s="175"/>
-      <c r="M62" s="175"/>
+      <c r="J62"/>
+      <c r="K62" s="57"/>
+      <c r="L62"/>
+      <c r="M62"/>
       <c r="N62"/>
       <c r="O62"/>
       <c r="P62"/>
@@ -3867,10 +3721,10 @@
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63"/>
-      <c r="J63" s="175"/>
-      <c r="K63" s="176"/>
-      <c r="L63" s="175"/>
-      <c r="M63" s="175"/>
+      <c r="J63"/>
+      <c r="K63" s="57"/>
+      <c r="L63"/>
+      <c r="M63"/>
       <c r="N63"/>
       <c r="O63"/>
       <c r="P63"/>
@@ -3888,10 +3742,10 @@
       <c r="G64"/>
       <c r="H64"/>
       <c r="I64"/>
-      <c r="J64" s="175"/>
-      <c r="K64" s="176"/>
-      <c r="L64" s="175"/>
-      <c r="M64" s="175"/>
+      <c r="J64"/>
+      <c r="K64" s="57"/>
+      <c r="L64"/>
+      <c r="M64"/>
       <c r="N64"/>
       <c r="O64"/>
       <c r="P64"/>
@@ -3900,34 +3754,19 @@
       <c r="T64"/>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J65" s="175"/>
-      <c r="K65" s="176"/>
-      <c r="L65" s="175"/>
-      <c r="M65" s="175"/>
+      <c r="K65" s="57"/>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J66" s="175"/>
-      <c r="K66" s="176"/>
-      <c r="L66" s="175"/>
-      <c r="M66" s="175"/>
+      <c r="K66" s="57"/>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J67" s="175"/>
-      <c r="K67" s="177"/>
-      <c r="L67" s="175"/>
-      <c r="M67" s="175"/>
+      <c r="K67" s="41"/>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J68" s="175"/>
-      <c r="K68" s="177"/>
-      <c r="L68" s="175"/>
-      <c r="M68" s="175"/>
+      <c r="K68" s="41"/>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J69" s="175"/>
-      <c r="K69" s="177"/>
-      <c r="L69" s="175"/>
-      <c r="M69" s="175"/>
+      <c r="K69" s="41"/>
     </row>
     <row r="70" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
@@ -3939,10 +3778,10 @@
       <c r="G70"/>
       <c r="H70"/>
       <c r="I70"/>
-      <c r="J70" s="175"/>
-      <c r="K70" s="177"/>
-      <c r="L70" s="178"/>
-      <c r="M70" s="175"/>
+      <c r="J70"/>
+      <c r="K70" s="41"/>
+      <c r="L70" s="58"/>
+      <c r="M70"/>
       <c r="N70"/>
       <c r="O70"/>
       <c r="P70"/>
@@ -3960,10 +3799,10 @@
       <c r="G71"/>
       <c r="H71"/>
       <c r="I71"/>
-      <c r="J71" s="175"/>
-      <c r="K71" s="175"/>
-      <c r="L71" s="178"/>
-      <c r="M71" s="175"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71" s="58"/>
+      <c r="M71"/>
       <c r="N71"/>
       <c r="O71"/>
       <c r="P71"/>
@@ -3971,96 +3810,64 @@
       <c r="R71"/>
       <c r="T71"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J72" s="175"/>
-      <c r="K72" s="175"/>
-      <c r="L72" s="175"/>
-      <c r="M72" s="175"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J73" s="175"/>
-      <c r="K73" s="175"/>
-      <c r="L73" s="175"/>
-      <c r="M73" s="175"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="J74" s="175"/>
-      <c r="K74" s="175"/>
-      <c r="L74" s="175"/>
-      <c r="M74" s="175"/>
-    </row>
   </sheetData>
   <mergeCells count="140">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="E2:M2"/>
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="M13:R13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="M57:O57"/>
+    <mergeCell ref="P57:R57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="M58:O58"/>
+    <mergeCell ref="P58:R58"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="P56:R56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="M55:O55"/>
+    <mergeCell ref="P55:R55"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="Q52:R52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="Q51:R51"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="Q22:R22"/>
     <mergeCell ref="B23:F23"/>
@@ -4075,62 +3882,76 @@
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="Q21:R21"/>
     <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="Q46:R46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="Q47:R47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="Q48:R48"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="Q53:R53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="Q54:R54"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="Q51:R51"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="P56:R56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="M55:O55"/>
-    <mergeCell ref="P55:R55"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="M57:O57"/>
-    <mergeCell ref="P57:R57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="M58:O58"/>
-    <mergeCell ref="P58:R58"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="M13:R13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="E2:M2"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:R4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.05" right="0" top="0.5" bottom="0.05" header="0" footer="0"/>

--- a/ReferenceFiles/Sample Job Costing Sheet.xlsx
+++ b/ReferenceFiles/Sample Job Costing Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhatia\Desktop\CostEstimatorAgent\ReferenceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF000AEB-4B76-407E-9453-FD2B585BE857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C494605E-C6B8-43EC-8A53-36BD9BFEAA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="142676- Structure Frame" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="89">
   <si>
     <t>C&amp;J GULF EQUIPMENT MANUFACTURING L.L.C</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>Kg</t>
-  </si>
-  <si>
-    <t>Paint Material</t>
   </si>
   <si>
     <t>litres</t>
@@ -1408,9 +1405,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1521,6 +1515,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="3" borderId="36" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1967,7 +1964,7 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="64"/>
       <c r="C3" s="64"/>
@@ -2540,7 +2537,7 @@
         <v>5.2</v>
       </c>
       <c r="B24" s="131" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="132"/>
       <c r="D24" s="132"/>
@@ -2548,7 +2545,7 @@
       <c r="F24" s="133"/>
       <c r="G24" s="51"/>
       <c r="H24" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I24" s="24"/>
       <c r="J24" s="25">
@@ -2570,16 +2567,17 @@
       <c r="A25" s="50">
         <v>5.3</v>
       </c>
-      <c r="B25" s="134" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="135"/>
-      <c r="D25" s="135"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="136"/>
+      <c r="B25" s="171">
+        <f>J32</f>
+        <v>9.5</v>
+      </c>
+      <c r="C25" s="134"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="135"/>
       <c r="G25" s="51"/>
       <c r="H25" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="25">
@@ -2602,7 +2600,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="128" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="129"/>
       <c r="D26" s="129"/>
@@ -2656,12 +2654,12 @@
         <v>7</v>
       </c>
       <c r="B28" s="116" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="117"/>
       <c r="D28" s="117"/>
       <c r="E28" s="117"/>
-      <c r="F28" s="140"/>
+      <c r="F28" s="139"/>
       <c r="G28" s="23"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
@@ -2682,19 +2680,19 @@
       <c r="A29" s="29">
         <v>7.1</v>
       </c>
-      <c r="B29" s="137" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="138" t="s">
+      <c r="B29" s="136" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="138" t="s">
+      <c r="D29" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="138" t="s">
+      <c r="E29" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="139"/>
+      <c r="F29" s="138"/>
       <c r="G29" s="51"/>
       <c r="H29" s="24" t="s">
         <v>40</v>
@@ -2723,19 +2721,19 @@
       <c r="A30" s="29">
         <v>7.2</v>
       </c>
-      <c r="B30" s="137" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="138" t="s">
+      <c r="B30" s="136" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="138" t="s">
+      <c r="D30" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="138" t="s">
+      <c r="E30" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="139"/>
+      <c r="F30" s="138"/>
       <c r="G30" s="51"/>
       <c r="H30" s="24" t="s">
         <v>40</v>
@@ -2764,16 +2762,16 @@
       <c r="A31" s="29">
         <v>7.3</v>
       </c>
-      <c r="B31" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="142"/>
-      <c r="D31" s="142"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="142"/>
+      <c r="B31" s="140" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
       <c r="G31" s="34"/>
       <c r="H31" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I31" s="48"/>
       <c r="J31" s="31">
@@ -2799,13 +2797,13 @@
       <c r="A32" s="29">
         <v>7.4</v>
       </c>
-      <c r="B32" s="137" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
+      <c r="B32" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
       <c r="G32" s="23"/>
       <c r="H32" s="24" t="s">
         <v>40</v>
@@ -2831,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
@@ -2863,7 +2861,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="117"/>
       <c r="D34" s="117"/>
@@ -2889,16 +2887,16 @@
       <c r="A35" s="29">
         <v>9.1</v>
       </c>
-      <c r="B35" s="137" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
+      <c r="B35" s="136" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
       <c r="G35" s="23"/>
       <c r="H35" s="24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I35" s="24"/>
       <c r="J35" s="25">
@@ -2922,7 +2920,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="116" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="117"/>
       <c r="D36" s="117"/>
@@ -2949,16 +2947,16 @@
       <c r="A37" s="29">
         <v>10.1</v>
       </c>
-      <c r="B37" s="137" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="138"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="139"/>
+      <c r="B37" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="138"/>
       <c r="G37" s="34"/>
       <c r="H37" s="35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="31">
@@ -2981,7 +2979,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="116" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="117"/>
       <c r="D38" s="117"/>
@@ -3007,13 +3005,13 @@
       <c r="A39" s="29">
         <v>11.1</v>
       </c>
-      <c r="B39" s="137" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="138"/>
-      <c r="D39" s="138"/>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
+      <c r="B39" s="136" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
       <c r="G39" s="23"/>
       <c r="H39" s="24" t="s">
         <v>40</v>
@@ -3042,16 +3040,16 @@
       <c r="A40" s="29">
         <v>11.2</v>
       </c>
-      <c r="B40" s="143" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" s="144"/>
-      <c r="D40" s="144"/>
-      <c r="E40" s="144"/>
-      <c r="F40" s="144"/>
+      <c r="B40" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="143"/>
+      <c r="D40" s="143"/>
+      <c r="E40" s="143"/>
+      <c r="F40" s="143"/>
       <c r="G40" s="34"/>
       <c r="H40" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I40" s="37"/>
       <c r="J40" s="31">
@@ -3077,16 +3075,16 @@
       <c r="A41" s="29">
         <v>11.3</v>
       </c>
-      <c r="B41" s="143" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="144"/>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
+      <c r="B41" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="143"/>
+      <c r="D41" s="143"/>
+      <c r="E41" s="143"/>
+      <c r="F41" s="143"/>
       <c r="G41" s="34"/>
       <c r="H41" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I41" s="37"/>
       <c r="J41" s="31">
@@ -3110,7 +3108,7 @@
         <v>12</v>
       </c>
       <c r="B42" s="116" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" s="117"/>
       <c r="D42" s="117"/>
@@ -3139,7 +3137,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="116" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" s="117"/>
       <c r="D43" s="117"/>
@@ -3170,7 +3168,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="116" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" s="117"/>
       <c r="D44" s="117"/>
@@ -3178,7 +3176,7 @@
       <c r="F44" s="117"/>
       <c r="G44" s="23"/>
       <c r="H44" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="25">
@@ -3202,7 +3200,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" s="22"/>
       <c r="D45" s="22"/>
@@ -3232,7 +3230,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="116" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" s="117"/>
       <c r="D46" s="117"/>
@@ -3240,7 +3238,7 @@
       <c r="F46" s="117"/>
       <c r="G46" s="23"/>
       <c r="H46" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="25"/>
@@ -3262,7 +3260,7 @@
         <v>18</v>
       </c>
       <c r="B47" s="116" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="117"/>
       <c r="D47" s="117"/>
@@ -3292,7 +3290,7 @@
         <v>20</v>
       </c>
       <c r="B48" s="116" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C48" s="117"/>
       <c r="D48" s="117"/>
@@ -3322,7 +3320,7 @@
         <v>21</v>
       </c>
       <c r="B49" s="116" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49" s="117"/>
       <c r="D49" s="117"/>
@@ -3352,7 +3350,7 @@
         <v>22</v>
       </c>
       <c r="B50" s="116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50" s="117"/>
       <c r="D50" s="117"/>
@@ -3382,7 +3380,7 @@
         <v>23</v>
       </c>
       <c r="B51" s="116" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51" s="117"/>
       <c r="D51" s="117"/>
@@ -3412,7 +3410,7 @@
         <v>24</v>
       </c>
       <c r="B52" s="116" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="117"/>
       <c r="D52" s="117"/>
@@ -3442,7 +3440,7 @@
         <v>25</v>
       </c>
       <c r="B53" s="116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" s="117"/>
       <c r="D53" s="117"/>
@@ -3472,7 +3470,7 @@
         <v>26</v>
       </c>
       <c r="B54" s="116" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="117"/>
       <c r="D54" s="117"/>
@@ -3501,111 +3499,111 @@
       </c>
     </row>
     <row r="55" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="151" t="s">
+      <c r="A55" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="B55" s="152"/>
-      <c r="C55" s="152"/>
-      <c r="D55" s="153">
+      <c r="B55" s="151"/>
+      <c r="C55" s="151"/>
+      <c r="D55" s="152">
         <f>SUM(K16:K54)</f>
         <v>0</v>
       </c>
-      <c r="E55" s="154"/>
-      <c r="F55" s="155"/>
-      <c r="G55" s="156" t="s">
-        <v>71</v>
-      </c>
-      <c r="H55" s="156"/>
+      <c r="E55" s="153"/>
+      <c r="F55" s="154"/>
+      <c r="G55" s="155" t="s">
+        <v>70</v>
+      </c>
+      <c r="H55" s="155"/>
       <c r="I55" s="41"/>
       <c r="J55" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K55" s="56"/>
       <c r="L55" s="52"/>
-      <c r="M55" s="157" t="s">
+      <c r="M55" s="156" t="s">
+        <v>72</v>
+      </c>
+      <c r="N55" s="157"/>
+      <c r="O55" s="157"/>
+      <c r="P55" s="158" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q55" s="156"/>
+      <c r="R55" s="159"/>
+    </row>
+    <row r="56" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="144" t="s">
         <v>73</v>
       </c>
-      <c r="N55" s="158"/>
-      <c r="O55" s="158"/>
-      <c r="P55" s="159" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q55" s="157"/>
-      <c r="R55" s="160"/>
-    </row>
-    <row r="56" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="145" t="s">
+      <c r="B56" s="145"/>
+      <c r="C56" s="145"/>
+      <c r="D56" s="146">
+        <f>S54</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="147"/>
+      <c r="F56" s="148"/>
+      <c r="G56" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="146"/>
-      <c r="C56" s="146"/>
-      <c r="D56" s="147">
-        <f>S54</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="148"/>
-      <c r="F56" s="149"/>
-      <c r="G56" s="150" t="s">
-        <v>75</v>
-      </c>
-      <c r="H56" s="150"/>
+      <c r="H56" s="149"/>
       <c r="I56" s="42"/>
       <c r="J56" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K56" s="56"/>
       <c r="L56" s="52"/>
-      <c r="M56" s="150" t="s">
+      <c r="M56" s="149" t="s">
+        <v>74</v>
+      </c>
+      <c r="N56" s="149"/>
+      <c r="O56" s="149"/>
+      <c r="P56" s="68" t="s">
         <v>75</v>
-      </c>
-      <c r="N56" s="150"/>
-      <c r="O56" s="150"/>
-      <c r="P56" s="68" t="s">
-        <v>76</v>
       </c>
       <c r="Q56" s="69"/>
       <c r="R56" s="73"/>
     </row>
     <row r="57" spans="1:20" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="161" t="s">
-        <v>77</v>
-      </c>
-      <c r="B57" s="162"/>
-      <c r="C57" s="162"/>
-      <c r="D57" s="163">
+      <c r="A57" s="160" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" s="161"/>
+      <c r="C57" s="161"/>
+      <c r="D57" s="162">
         <f>D55+D56</f>
         <v>0</v>
       </c>
-      <c r="E57" s="164"/>
-      <c r="F57" s="165"/>
+      <c r="E57" s="163"/>
+      <c r="F57" s="164"/>
       <c r="G57" s="43"/>
       <c r="H57" s="43"/>
       <c r="I57" s="43"/>
       <c r="J57" s="5"/>
       <c r="K57" s="56"/>
       <c r="L57" s="52"/>
-      <c r="M57" s="166" t="s">
+      <c r="M57" s="165" t="s">
+        <v>77</v>
+      </c>
+      <c r="N57" s="149"/>
+      <c r="O57" s="166"/>
+      <c r="P57" s="68" t="s">
         <v>78</v>
-      </c>
-      <c r="N57" s="150"/>
-      <c r="O57" s="167"/>
-      <c r="P57" s="68" t="s">
-        <v>79</v>
       </c>
       <c r="Q57" s="69"/>
       <c r="R57" s="73"/>
     </row>
     <row r="58" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="161" t="s">
-        <v>80</v>
-      </c>
-      <c r="B58" s="162"/>
-      <c r="C58" s="162"/>
-      <c r="D58" s="163"/>
-      <c r="E58" s="164"/>
-      <c r="F58" s="165"/>
-      <c r="G58" s="168"/>
-      <c r="H58" s="168"/>
+      <c r="A58" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" s="161"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="162"/>
+      <c r="E58" s="163"/>
+      <c r="F58" s="164"/>
+      <c r="G58" s="167"/>
+      <c r="H58" s="167"/>
       <c r="I58" s="43"/>
       <c r="J58" s="5"/>
       <c r="K58" s="56"/>
@@ -3613,23 +3611,20 @@
       <c r="M58" s="68"/>
       <c r="N58" s="69"/>
       <c r="O58" s="73"/>
-      <c r="P58" s="169"/>
-      <c r="Q58" s="170"/>
-      <c r="R58" s="171"/>
+      <c r="P58" s="168"/>
+      <c r="Q58" s="169"/>
+      <c r="R58" s="170"/>
       <c r="T58"/>
     </row>
     <row r="59" spans="1:20" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="161" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" s="162"/>
-      <c r="C59" s="162"/>
-      <c r="D59" s="163">
-        <f>+D58-D57</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="164"/>
-      <c r="F59" s="165"/>
+      <c r="A59" s="160" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="161"/>
+      <c r="C59" s="161"/>
+      <c r="D59" s="162"/>
+      <c r="E59" s="163"/>
+      <c r="F59" s="164"/>
       <c r="G59"/>
       <c r="H59"/>
       <c r="I59"/>
